--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-03-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-03-2026.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/25mm-celotex-tb3025-2-4m-x-1-2m</t>
+          <t>£10.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://www.planetinsulation.co.uk/products/celotex-pir-tb-ga-xr?_pos=1&amp;_sid=22d5094c4&amp;_ss=r</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£27.67</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£46.64</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£0.0</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£0.0</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£89.87</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£0.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
